--- a/submission/ADI-FY2026Q3.xlsx
+++ b/submission/ADI-FY2026Q3.xlsx
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C7" s="54" t="n">
-        <v>4008</v>
+        <v>4009.6</v>
       </c>
     </row>
     <row r="8" ht="29" customHeight="1">
